--- a/data/trans_bre/P16A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 16,93</t>
+          <t>10,13; 16,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 19,94</t>
+          <t>12,35; 20,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 22,07</t>
+          <t>13,01; 21,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,64; 29,9</t>
+          <t>20,53; 29,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,3; 102,11</t>
+          <t>48,45; 98,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,66; 88,67</t>
+          <t>45,37; 90,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,93; 102,42</t>
+          <t>49,3; 97,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,24; 96,7</t>
+          <t>54,07; 95,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,35</t>
+          <t>4,47; 9,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 15,95</t>
+          <t>10,33; 16,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 12,72</t>
+          <t>7,54; 12,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 38,67</t>
+          <t>10,88; 34,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,98; 89,02</t>
+          <t>35,58; 85,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,91; 106,24</t>
+          <t>58,98; 109,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,31; 80,4</t>
+          <t>40,82; 81,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,79; 225,99</t>
+          <t>47,92; 196,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 12,3</t>
+          <t>3,34; 12,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 21,07</t>
+          <t>10,75; 21,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 13,02</t>
+          <t>2,62; 13,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 14,65</t>
+          <t>4,96; 14,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,49; 129,46</t>
+          <t>23,92; 127,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,93; 249,45</t>
+          <t>82,9; 236,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 82,26</t>
+          <t>12,68; 84,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 87,35</t>
+          <t>21,83; 84,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,95</t>
+          <t>8,02; 11,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 17,61</t>
+          <t>13,41; 17,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,59</t>
+          <t>10,06; 14,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 32,33</t>
+          <t>14,38; 31,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,56; 92,27</t>
+          <t>54,04; 91,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,42; 104,51</t>
+          <t>71,06; 104,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,42; 83,26</t>
+          <t>50,61; 81,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,35; 159,02</t>
+          <t>58,43; 162,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,45</t>
+          <t>25,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 16,93</t>
+          <t>9,77; 16,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,35; 20,3</t>
+          <t>11,59; 19,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 21,91</t>
+          <t>13,29; 22,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,53; 29,95</t>
+          <t>21,8; 30,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,45; 98,94</t>
+          <t>47,54; 100,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,37; 90,15</t>
+          <t>42,62; 89,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,3; 97,75</t>
+          <t>50,39; 102,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,07; 95,25</t>
+          <t>59,84; 100,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,0</t>
+          <t>11,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,13</t>
+          <t>4,16; 9,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,33; 16,18</t>
+          <t>10,77; 16,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,86</t>
+          <t>7,76; 13,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,88; 34,1</t>
+          <t>9,47; 14,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,58; 85,33</t>
+          <t>31,81; 88,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,98; 109,01</t>
+          <t>61,67; 106,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,82; 81,49</t>
+          <t>42,36; 81,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,92; 196,36</t>
+          <t>39,52; 71,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>9,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,63</t>
+          <t>3,34; 12,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 21,19</t>
+          <t>10,67; 21,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 13,12</t>
+          <t>2,66; 12,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,55</t>
+          <t>4,73; 13,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,92; 127,47</t>
+          <t>25,82; 124,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,9; 236,66</t>
+          <t>82,48; 248,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 84,24</t>
+          <t>13,02; 79,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,83; 84,79</t>
+          <t>21,4; 79,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,48</t>
+          <t>15,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,84</t>
+          <t>7,95; 11,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 17,72</t>
+          <t>13,43; 17,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 14,42</t>
+          <t>10,37; 14,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 31,72</t>
+          <t>13,02; 17,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,04; 91,16</t>
+          <t>54,29; 88,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,06; 104,64</t>
+          <t>70,93; 105,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,61; 81,04</t>
+          <t>52,16; 80,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,43; 162,28</t>
+          <t>51,68; 77,4</t>
         </is>
       </c>
     </row>
